--- a/outputs/resultats/bnc/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/resultats/bnc/2026_t1_vs_2025_t3/comparison.xlsx
@@ -587,7 +587,9 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Cet indicateur a été ajouté pour répondre aux exigences de divulgation réglementaire concernant la gestion des risques de liquidité.</t>
+          <t>L'indicateur "Ratio de liquidité à court terme" a été ajouté dans le tableau des actifs grevés et non grevés au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout est significatif car le ratio de liquidité à court terme est un indicateur clé de la capacité d'une institution financière à couvrir ses obligations à court terme avec ses actifs liquides. Il est souvent utilisé dans le cadre des exigences de Bâle III pour évaluer la résilience financière d'une banque face à des chocs de liquidité. La présence de ce ratio dans le tableau renforce la transparence et la conformité réglementaire.
+Il s'agit d'une nouvelle divulgation réglementaire. L'analyste devrait confirmer que les valeurs divulguées sont cohérentes avec les autres tableaux de liquidité du rapport et vérifier l'alignement avec les exigences de Bâle III.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -596,21 +598,9 @@
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:01:12.767857+00:00</t>
-        </is>
-      </c>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -625,12 +615,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -645,17 +635,19 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Pour de plus amples renseignements, se reporter aux notes 18 et 19 afférentes aux états financiers annuels consolidés audités de l’exercice terminé le 31 octobre 2024.</t>
+          <t>Ces montants incluent 48,6 G$ révocables sans condition en tout temps à la discrétion de la Banque.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Pour de plus amples renseignements, se reporter aux notes 17 et 18 afférentes aux états financiers annuels consolidés audités de l’exercice terminé le 31 octobre 2025.</t>
+          <t>Ces montants incluent 57,2 G$ révocables sans condition en tout temps à la discrétion de la Banque.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>La modification des numéros de notes référencées peut indiquer un changement dans la structure ou le contenu des états financiers, ce qui nécessite une attention particulière pour comprendre l'impact potentiel sur l'analyse financière.</t>
+          <t>La note de bas de page n°8 a été modifiée dans le tableau des échéances contractuelles des passifs, capitaux propres et engagements hors bilan. Le texte a été révisé pour indiquer que les montants incluent désormais 57,2 G$ au lieu de 48,6 G$, toujours révocables sans condition à la discrétion de la Banque.
+L'impact de cette modification est significatif car elle reflète une augmentation substantielle des montants révocables, ce qui peut avoir des implications sur la liquidité et la gestion des risques de la banque. Cette révision pourrait être liée à des ajustements dans les politiques de gestion des liquidités ou à des changements dans les conditions de marché. Elle pourrait également affecter les ratios de liquidité réglementaires tels que le LCR (Liquidity Coverage Ratio) sous Bâle III.
+Il s'agit d'une mise à jour importante qui pourrait indiquer un changement dans la stratégie de gestion des liquidités de la banque. L'analyste devrait investiguer les raisons de cette augmentation et s'assurer que cela est cohérent avec les autres informations financières et de risque présentées dans le rapport.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -664,21 +656,9 @@
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:00:51.765920+00:00</t>
-        </is>
-      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -693,12 +673,12 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -708,22 +688,20 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Pour de plus amples renseignements, se reporter à la note 25 afférente aux états financiers annuels consolidés audités de l’exercice terminé le 31 octobre 2024.</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Pour de plus amples renseignements, se reporter à la note 23 afférente aux états financiers annuels consolidés audités de l’exercice terminé le 31 octobre 2025.</t>
-        </is>
-      </c>
+          <t>Le 3 février 2025, la Banque a conclu l’acquisition de CWB. Les résultats de CWB ont été consolidés à partir de la date de clôture, ce qui a eu une incidence sur les soldes au 31 juillet 2025. Consulter la section « Acquisition » pour de plus amples renseignements sur l’incidence de l’acquisition de CWB.</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr"/>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>La modification du numéro de note référencée peut refléter une réorganisation des informations financières, ce qui est crucial pour assurer la conformité et la précision des analyses.</t>
+          <t>La note de bas de page n°1 a été supprimée du tableau des échéances contractuelles des actifs financiers. Cette note faisait référence à l'acquisition de CWB par la Banque le 3 février 2025 et à l'impact de cette acquisition sur les soldes au 31 juillet 2025.
+L'absence de cette note dans le rapport actuel pourrait indiquer que l'impact de l'acquisition de CWB n'est plus pertinent pour la période actuelle ou que les informations ont été intégrées ailleurs dans le rapport. Cela pourrait avoir des implications sur la transparence des divulgations financières, notamment en ce qui concerne les exigences de Bâle III sur la consolidation des résultats financiers et la divulgation des événements significatifs.
+Il s'agit potentiellement d'une mise à jour ordinaire si l'acquisition n'a plus d'impact significatif sur les états financiers actuels. Cependant, l'analyste devrait confirmer que toutes les informations pertinentes concernant l'acquisition de CWB sont correctement divulguées ailleurs dans le rapport pour assurer la conformité réglementaire et la transparence.</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -732,66 +710,52 @@
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:03:40.590586+00:00</t>
-        </is>
-      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Actions, autres instruments de capitaux propres et options d’achat d’actions</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Ces montants incluent 48,6 G$ révocables sans condition en tout temps à la discrétion de la Banque.</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Ces montants incluent 57,2 G$ révocables sans condition en tout temps à la discrétion de la Banque.</t>
-        </is>
-      </c>
+          <t>BCRL – Série 1</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr"/>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>L'augmentation du montant révocable sans condition de 48,6 G$ à 57,2 G$ indique un changement significatif dans les engagements de la Banque, nécessitant une attention particulière pour l'analyse des risques.</t>
+          <t>L'indicateur 'BCRL – Série 1' a été retiré du tableau des actions, autres instruments de capitaux propres et options d’achat d’actions au T2 2025, alors qu'il était présent au T1 2025.
+Ce retrait peut indiquer un changement dans la structure du capital ou une modification des instruments financiers disponibles pour l'institution. Les BCRL (Billets à Capital Relevable et à Liquidité) sont souvent utilisés pour renforcer les fonds propres et répondre aux exigences de capital réglementaire, notamment celles définies par Bâle III et les lignes directrices du BSIF. L'absence de cet instrument pourrait signaler une stratégie de financement modifiée ou une restructuration des obligations de capital.
+Il s'agit d'un changement structurel potentiellement significatif. L'analyste devrait investiguer les raisons de ce retrait, vérifier s'il y a eu une substitution par un autre instrument ou une modification de la stratégie de capital, et s'assurer que cela n'affecte pas la conformité réglementaire.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -800,41 +764,29 @@
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:03:18.433042+00:00</t>
-        </is>
-      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Capital réglementaire (1), ratio de levier (1) et TLAC (2)</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -844,18 +796,20 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Les montants remboursables sur demande sont considérés comme étant sans échéance spécifique.</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Les données au 31 octobre 2025 tenaient compte du rachat des BCRL – Série 1 effectué le 17 novembre 2025.</t>
+        </is>
+      </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>La suppression de cette note peut affecter la compréhension des échéances des actifs financiers, car elle clarifiait le traitement des montants remboursables sur demande.</t>
+          <t>La note de bas de page n-3 a été ajoutée dans le tableau de gestion du capital au T1 2026.
+Cette note précise que les données au 31 octobre 2025 incluaient l'impact du rachat des BCRL – Série 1 effectué le 17 novembre 2025. Cela indique une mise à jour importante des données financières historiques, ce qui peut affecter l'analyse des ratios de capital et de levier. Le rachat de titres de dette peut avoir un impact significatif sur les fonds propres réglementaires et les ratios de levier, en particulier si ces titres étaient comptabilisés dans les fonds propres de catégorie 1 ou 2.
+Il s'agit d'une mise à jour structurante qui pourrait influencer l'évaluation des risques et la gestion du capital. L'analyste devrait confirmer l'impact de ce rachat sur les ratios de capital et s'assurer que cette information est cohérente avec les autres divulgations financières du rapport.</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -864,62 +818,52 @@
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:01:00.996187+00:00</t>
-        </is>
-      </c>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>(sans titre)</t>
+          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>Ces montants incluent 5 M$ d’engagements contractuels liés à l’immeuble du siège social.</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Activité de paiement (7)</t>
+        </is>
+      </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>La suppression de cette note supprime une divulgation importante concernant les engagements contractuels liés à l'immeuble du siège social, ce qui pourrait affecter la transparence des informations financières.</t>
+          <t>L'indicateur 'Activité de paiement (7)' a été ajouté dans le tableau des indicateurs BISM au T2 2025, alors qu'il était absent au T1 2025.
+Cet ajout pourrait refléter une nouvelle exigence de divulgation ou une mise à jour des pratiques de reporting pour inclure des aspects plus détaillés de l'activité bancaire, notamment en ce qui concerne les paiements. Les paiements sont un élément crucial de l'infrastructure financière et leur inclusion pourrait être liée à des directives récentes sur la transparence et la gestion des risques opérationnels.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cet ajout est conforme aux nouvelles directives réglementaires ou aux meilleures pratiques de l'industrie.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -940,7 +884,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>2026-04-18T18:04:06.288719+00:00</t>
+          <t>2026-04-23T20:05:06.912104+00:00</t>
         </is>
       </c>
     </row>
@@ -952,17 +896,17 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Actions, autres instruments de capitaux propres et options d’achat d’actions</t>
+          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -972,18 +916,20 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>BCRL – Série 1</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Volume des transactions (8)</t>
+        </is>
+      </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>La suppression de cet indicateur peut indiquer un changement dans la structure des instruments de capitaux propres, ce qui pourrait affecter l'analyse des fonds propres réglementaires.</t>
+          <t>L'indicateur 'Volume des transactions (8)' a été ajouté dans le tableau des indicateurs BISM au T2 2025, alors qu'il était absent au T1 2025.
+Le volume des transactions est un indicateur essentiel pour évaluer l'activité opérationnelle d'une banque, en particulier dans le contexte des marchés financiers. Cet ajout pourrait être motivé par des exigences de transparence accrues ou des changements dans les pratiques de reporting pour mieux capturer l'activité transactionnelle.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que cet ajout est conforme aux nouvelles exigences de divulgation ou aux meilleures pratiques de l'industrie.</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -992,9 +938,21 @@
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Validé</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>analyst</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-23T20:05:07.121199+00:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1004,22 +962,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Capital réglementaire (1), ratio de levier (1) et TLAC (2)</t>
+          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1030,12 +988,14 @@
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>Les données au 31 octobre 2025 tenaient compte du rachat des BCRL – Série 1 effectué le 17 novembre 2025.</t>
+          <t>Titres à revenu fixe (8)</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Cette note a été ajoutée pour indiquer un événement significatif, le rachat des BCRL, qui peut avoir un impact sur les ratios financiers présentés. Cela est important pour l'analyse des changements structurels dans les fonds propres.</t>
+          <t>L'indicateur 'Titres à revenu fixe (8)' apparaît dans le tableau des indicateurs BISM au T2 2025, sans équivalent direct au T1 2025.
+Les titres à revenu fixe sont un élément clé des portefeuilles d'investissement des banques et leur inclusion dans le tableau pourrait refléter une nouvelle exigence de divulgation pour mieux comprendre la composition et le risque des actifs détenus par la banque. Cela pourrait être en réponse à des directives récentes sur la gestion des risques de marché.
+Cet ajout représente une mise à jour structurelle significative. L'analyste devrait s'assurer que cet indicateur est aligné avec les nouvelles normes de divulgation ou les attentes des régulateurs.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1082,12 +1042,14 @@
       <c r="G10" s="3" t="inlineStr"/>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>Activité de paiement (7)</t>
+          <t>Titres de participation et autres titres (8)</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>Cet indicateur a été ajouté pour mieux refléter l'activité de paiement, ce qui est crucial pour évaluer l'impact systémique des banques.</t>
+          <t>L'indicateur 'Titres de participation et autres titres (8)' est présent dans le tableau des indicateurs BISM au T2 2025, mais n'était pas inclus au T1 2025.
+Cet indicateur est crucial pour évaluer l'exposition d'une banque aux marchés actions et autres instruments financiers. Son inclusion pourrait être motivée par des exigences accrues de transparence ou de gestion des risques liés aux investissements en actions, en ligne avec les recommandations du Comité de Bâle.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier si cet indicateur est aligné avec les nouvelles normes de divulgation ou les attentes des régulateurs.</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1096,21 +1058,9 @@
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>Rejeté</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:02:07.843565+00:00</t>
-        </is>
-      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1140,18 +1090,20 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>Volume des transactions (8)</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Substituabilité/infrastructure financière (7)</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr"/>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>L'ajout de cet indicateur permet de suivre le volume des transactions, ce qui est crucial pour l'analyse de la liquidité.</t>
+          <t>L'indicateur 'Substituabilité/infrastructure financière (7)' était présent dans le tableau des indicateurs BISM au T1 2025, mais a été retiré au T2 2025.
+Cet indicateur est important pour évaluer la capacité d'une banque à être remplacée par d'autres institutions en cas de défaillance, ce qui est un aspect clé de l'évaluation de l'importance systémique. Son retrait pourrait indiquer un changement dans les priorités de divulgation ou une révision des méthodologies d'évaluation de l'importance systémique.
+Il s'agit d'une mise à jour structurelle significative. L'analyste devrait investiguer les raisons de ce retrait et s'assurer qu'il est conforme aux nouvelles directives réglementaires ou aux meilleures pratiques de l'industrie.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1160,21 +1112,9 @@
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Rejeté</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:02:13.476478+00:00</t>
-        </is>
-      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1199,23 +1139,25 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Indicateur</t>
+          <t>Note de bas de page</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Ajout</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>Titres à revenu fixe (8)</t>
-        </is>
-      </c>
+          <t>Suppression</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Les montants au 31 octobre 2024 ont été révisés par rapport à ceux présentés précédemment.</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr"/>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Cet indicateur est important pour évaluer l'exposition aux titres à revenu fixe, influençant la stabilité financière.</t>
+          <t>La note de bas de page n°3, qui indiquait que les montants au 31 octobre 2024 avaient été révisés par rapport à ceux présentés précédemment, a été supprimée dans le tableau des indicateurs BISM.
+Cette note était cruciale pour signaler aux utilisateurs du rapport que des ajustements avaient été effectués sur les données financières d'une période antérieure. La suppression de cette note pourrait indiquer que les révisions ont été intégrées et ne nécessitent plus de mention explicite, ou que les ajustements ont été finalisés et validés.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que la suppression de cette note est justifiée par la stabilisation des données révisées et qu'elle est conforme aux pratiques de divulgation financière.</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1224,21 +1166,9 @@
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>Rejeté</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:02:14.759591+00:00</t>
-        </is>
-      </c>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -1248,17 +1178,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1274,12 +1204,14 @@
       <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Titres de participation et autres titres (8)</t>
+          <t>Risque opérationnel – Variation des niveaux de risque</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>L'ajout de cet indicateur permet de mieux comprendre l'exposition aux titres de participation, ce qui est crucial pour l'évaluation des risques.</t>
+          <t>L'indicateur "Risque opérationnel – Variation des niveaux de risque" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
+La gestion du risque opérationnel est un aspect fondamental des exigences de Bâle III, qui vise à garantir que les institutions financières disposent de fonds propres suffisants pour couvrir les pertes potentielles dues à des événements opérationnels. La divulgation de cet indicateur permet une meilleure évaluation des variations de risque opérationnel et contribue à la transparence des pratiques de gestion des risques.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que cet ajout est cohérent avec les autres divulgations de risques opérationnels et vérifier si des ajustements méthodologiques ont été effectués.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1288,21 +1220,9 @@
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Rejeté</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:02:15.487478+00:00</t>
-        </is>
-      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1312,42 +1232,40 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Les montants au 31 octobre 2024 ont été révisés par rapport à ceux présentés précédemment.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>Représente le total des expositions au bilan et hors bilan de la Banque selon les règles de ratio de levier du BSIF en vertu de l’accord de Bâle III, avant ajustements réglementaires.</t>
+          <t>Risque opérationnel – Méthode et politique</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>La reformulation de cette note modifie la compréhension des expositions au bilan et hors bilan, ce qui est crucial pour l'évaluation des ratios de levier et de la conformité réglementaire.</t>
+          <t>L'indicateur "Risque opérationnel – Méthode et politique" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
+Les méthodes et politiques de gestion du risque opérationnel sont essentielles pour assurer une gestion efficace et conforme aux exigences réglementaires. Bâle III met l'accent sur l'importance d'une approche méthodologique rigoureuse pour évaluer et gérer les risques opérationnels. La divulgation de cet indicateur renforce la transparence et permet aux parties prenantes de mieux comprendre les approches adoptées par l'institution.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait s'assurer que les méthodes et politiques divulguées sont conformes aux normes réglementaires et aux meilleures pratiques du secteur.</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1356,21 +1274,9 @@
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:02:39.689195+00:00</t>
-        </is>
-      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1380,42 +1286,40 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>Représente le total des expositions au bilan et hors bilan de la Banque selon les règles de ratio de levier du BSIF en vertu de l’accord de Bâle III, avant ajustements réglementaires.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>Incluant les activités d’assurances.</t>
+          <t>Risque opérationnel – Acquisitions et cessions</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>La modification de cette note pour inclure les activités d'assurances change la portée des expositions considérées, ce qui est essentiel pour l'analyse des risques.</t>
+          <t>L'indicateur "Risque opérationnel – Acquisitions et cessions" a été ajouté dans le tableau de gestion du capital au T2 2025, alors qu'il était absent au T1 2025.
+Les acquisitions et cessions peuvent avoir un impact significatif sur le profil de risque opérationnel d'une institution. En vertu des exigences de Bâle III, il est crucial de suivre et de divulguer ces changements pour évaluer correctement l'actif pondéré en fonction des risques. Cet indicateur permet de mieux comprendre comment les transactions stratégiques influencent les risques opérationnels.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait vérifier que les acquisitions et cessions sont correctement intégrées dans les calculs de risque et que les divulgations sont cohérentes avec les autres sections du rapport.</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1424,21 +1328,9 @@
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:02:54.530947+00:00</t>
-        </is>
-      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1448,17 +1340,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1468,22 +1360,20 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>Incluant les activités d’assurances.</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>Représente les transactions avec d’autres institutions financières.</t>
-        </is>
-      </c>
+          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisée conformément à l’approche utilisée par la Banque.</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr"/>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>La reformulation de cette note pour se concentrer sur les transactions interbancaires modifie l'analyse des relations financières et des risques de contrepartie.</t>
+          <t>La note de bas de page n°3 a été supprimée du tableau de gestion du capital au T2 2025. Cette note expliquait que la variation du risque opérationnel était liée à l'inclusion de CWB, calculée selon l'approche standardisée de la Banque.
+La suppression de cette note peut avoir des implications importantes sur la transparence des pratiques de gestion du risque opérationnel. En effet, l'inclusion de CWB et l'utilisation de l'approche standardisée sont des éléments clés pour comprendre comment les risques opérationnels sont évalués et intégrés dans les calculs de l'actif pondéré en fonction des risques. Cela est particulièrement pertinent dans le cadre des exigences de Bâle III, qui mettent l'accent sur la précision et la transparence des méthodes de calcul des risques.
+Il s'agit d'une mise à jour structurelle significative. L'analyste devrait investiguer les raisons de cette suppression et s'assurer que les informations sur l'inclusion de CWB et l'approche standardisée sont toujours disponibles sous une autre forme dans le rapport. Il est recommandé de vérifier la cohérence de cette suppression avec les autres divulgations de risques opérationnels.</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1492,21 +1382,9 @@
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:03:16.463376+00:00</t>
-        </is>
-      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1516,17 +1394,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1536,22 +1414,20 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Représente les transactions avec d’autres institutions financières.</t>
-        </is>
-      </c>
+          <t>Ajout</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>Représente la mesure dans laquelle les services de la Banque pourraient être remplacés par ceux d’autres institutions.</t>
+          <t>Le rachat des BCRL – Série 1 effectué le 17 novembre 2025 a été pris en compte dans les ratios au 31 octobre 2025.</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>La reformulation de cette note pour aborder la substituabilité des services bancaires modifie l'évaluation de la concurrence et des risques de marché.</t>
+          <t>La note de bas de page n°2 a été ajoutée dans le tableau des fonds propres réglementaires pour le trimestre terminé le 31 janvier 2026. Cette note précise que le rachat des BCRL – Série 1, effectué le 17 novembre 2025, a été pris en compte dans les ratios au 31 octobre 2025.
+L'ajout de cette note est significatif car il indique une mise à jour des ratios de fonds propres pour inclure l'impact d'un événement spécifique, à savoir le rachat des BCRL – Série 1. Cela peut avoir des implications sur les ratios de capital réglementaire, qui sont essentiels pour évaluer la solidité financière de la banque. Les exigences de Bâle III et les directives du BSIF sur les fonds propres réglementaires pourraient être directement concernées par cette mise à jour.
+Il s'agit d'une mise à jour structurelle importante. L'analyste devrait confirmer que l'impact de ce rachat est correctement reflété dans les autres sections du rapport et s'assurer que les calculs des ratios de capital sont conformes aux exigences réglementaires actuelles. Une vérification de la cohérence avec les autres divulgations financières est recommandée.</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1560,21 +1436,9 @@
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:04:01.877645+00:00</t>
-        </is>
-      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr"/>
+      <c r="N17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -1584,42 +1448,40 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>Pour les exercices terminés les 31 octobre 2024 et 2023.</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Cet indicateur est composé de deux sous-indicateurs : titres à revenu fixe ainsi que titres de participation et autres titres.</t>
-        </is>
-      </c>
+          <t>Émission d’actions ordinaires relatives à l'acquisition de CWB</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>La clarification de la composition de l'indicateur en sous-indicateurs spécifiques améliore la transparence et la compréhension des expositions aux titres.</t>
+          <t>L'indicateur "Émission d’actions ordinaires relatives à l'acquisition de CWB" a été retiré du tableau de synthèse des fonds propres réglementaires pour le trimestre terminé le 31 janvier 2026. Cet indicateur était présent dans le tableau précédent pour les neuf mois terminés le 31 juillet 2025.
+La suppression de cet indicateur pourrait indiquer que l'acquisition de CWB a été finalisée et que les émissions d'actions ordinaires associées ne sont plus pertinentes pour la période actuelle. Cela peut également refléter un changement dans la structure de capital ou une réorganisation des éléments de divulgation pour mieux aligner les rapports avec les exigences réglementaires actuelles.
+Il s'agit d'une mise à jour structurelle qui pourrait avoir des implications sur la compréhension des mouvements de capital par les parties prenantes. L'analyste devrait vérifier si cette suppression est cohérente avec les autres sections du rapport et s'assurer qu'il n'y a pas d'autres ajustements non divulgués liés à cette acquisition.</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1640,42 +1502,40 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
+          <t>Variation des fonds propres réglementaires (1)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>Note de bas de page</t>
+          <t>Indicateur</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>Cet indicateur est composé de deux sous-indicateurs : titres à revenu fixe ainsi que titres de participation et autres titres.</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>Tient compte du degré de complexité et du volume des activités de négociation de la Banque visant les instruments financiers dérivés, les titres détenus à des fins de négociation, les titres de placement et les actifs financiers de niveau 3.</t>
-        </is>
-      </c>
+          <t>Options de remplacement relatives à l'acquisition de CWB</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>La reformulation de cette note pour inclure la complexité et le volume des activités de négociation fournit une vue plus complète des risques associés aux instruments financiers.</t>
+          <t>L'indicateur "Options de remplacement relatives à l'acquisition de CWB" a été retiré du tableau de synthèse des fonds propres réglementaires pour le trimestre terminé le 31 janvier 2026. Cet indicateur était présent dans le tableau précédent pour les neuf mois terminés le 31 juillet 2025.
+La suppression de cet indicateur pourrait indiquer que les options de remplacement liées à l'acquisition de CWB ont été exercées ou ne sont plus pertinentes pour la période actuelle. Cela peut également refléter une simplification des rapports ou une réorganisation des éléments de divulgation pour mieux aligner les rapports avec les exigences réglementaires actuelles.
+Il s'agit d'une mise à jour structurelle qui pourrait avoir des implications sur la compréhension des mouvements de capital par les parties prenantes. L'analyste devrait vérifier si cette suppression est cohérente avec les autres sections du rapport et s'assurer qu'il n'y a pas d'autres ajustements non divulgués liés à cette acquisition.</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1689,256 +1549,248 @@
       <c r="N19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Indicateur</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter aux notes 18 et 19 afférentes aux états financiers annuels consolidés audités de l’exercice terminé le 31 octobre 2024.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter aux notes 17 et 18 afférentes aux états financiers annuels consolidés audités de l’exercice terminé le 31 octobre 2025.</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°7 a été modifiée pour refléter un changement dans la numérotation des notes référencées dans les états financiers consolidés annuels audités. Précédemment, elle faisait référence aux notes 18 et 19, tandis que dans la version actuelle, elle se réfère aux notes 17 et 18. Ce changement est purement technique et ne modifie pas le contenu ou l'interprétation des informations fournies.
+L'impact de ce changement est principalement cosmétique et n'affecte pas les ratios prudentiels ou les exigences de divulgation réglementaire. Il est important de noter que la renumérotation des notes dans les états financiers peut résulter de l'ajout ou de la suppression d'autres notes, mais cela n'implique pas nécessairement un changement dans les politiques comptables ou les méthodes de calcul.
+En conclusion, ce changement ne constitue pas une nouvelle divulgation ni une modification méthodologique. Il s'agit d'une mise à jour ordinaire de la documentation de référence. L'analyste peut confirmer ce changement sans nécessiter d'investigation supplémentaire.</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Modification</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter à la note 25 afférente aux états financiers annuels consolidés audités de l’exercice terminé le 31 octobre 2024.</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Pour de plus amples renseignements, se reporter à la note 23 afférente aux états financiers annuels consolidés audités de l’exercice terminé le 31 octobre 2025.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°8 a été modifiée pour refléter un changement dans la numérotation des notes référencées dans les états financiers consolidés annuels audités. Initialement, elle faisait référence à la note 25, tandis que dans la version actuelle, elle se réfère à la note 23. Ce changement est purement technique et ne modifie pas le contenu ou l'interprétation des informations fournies.
+L'impact de ce changement est principalement cosmétique et n'affecte pas les ratios prudentiels ou les exigences de divulgation réglementaire. Il est important de noter que la renumérotation des notes dans les états financiers peut résulter de l'ajout ou de la suppression d'autres notes, mais cela n'implique pas nécessairement un changement dans les politiques comptables ou les méthodes de calcul.
+En conclusion, ce changement ne constitue pas une nouvelle divulgation ni une modification méthodologique. Il s'agit d'une mise à jour ordinaire de la documentation de référence. L'analyste peut confirmer ce changement sans nécessiter d'investigation supplémentaire.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>(sans titre)</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Note de bas de page</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>Suppression</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Substituabilité/infrastructure financière (7)</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>La suppression de cet indicateur modifie la compréhension de la capacité de substitution et de l'infrastructure financière, ce qui peut affecter l'évaluation des risques systémiques.</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>Rejeté</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:02:16.049629+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Ces montants incluent 5 M$ d’engagements contractuels liés à l’immeuble du siège social.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>La note de bas de page n°10 a été retirée du tableau des échéances contractuelles des passifs, capitaux propres et engagements hors bilan. Cette note précisait que certains montants incluaient 5 M$ d’engagements contractuels liés à l’immeuble du siège social.
+L'impact de la suppression de cette note est probablement faible, car elle semble se rapporter à un montant spécifique et limité, lié à un actif particulier (l'immeuble du siège social). Il est possible que cette information ait été jugée non pertinente pour la période actuelle ou qu'elle ait été intégrée dans une autre section du rapport.
+Ce changement semble être une mise à jour ordinaire de la présentation des informations. L'analyste devrait confirmer que cette information n'est pas critique pour l'analyse des engagements de la banque et qu'elle est couverte ailleurs si nécessaire.</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Gestion des risques</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Note de bas de page</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>Tient compte du degré de complexité et du volume des activités de négociation de la Banque visant les instruments financiers dérivés, les titres détenus à des fins de négociation, les titres de placement et les actifs financiers de niveau 3.</t>
-        </is>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>La suppression de cette note supprime une divulgation importante sur la complexité et le volume des activités de négociation, ce qui peut affecter l'évaluation des risques associés aux instruments financiers dérivés.</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:02:37.495059+00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Variation de l’actif pondéré en fonction des risques selon les principaux facteurs (1)</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Suppression</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>Au cours du deuxième trimestre de 2025, la variation du risque opérationnel est liée à l’inclusion de CWB qui a été calculé selon l’approche standardisée conformément à l’approche utilisée par la Banque.</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr"/>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>La suppression de cette note pourrait indiquer un changement dans la manière dont le risque opérationnel est calculé ou rapporté, ce qui est crucial pour l'analyse des risques et la conformité réglementaire.</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>Gestion du capital</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Variation des fonds propres réglementaires (1)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Note de bas de page</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Ajout</t>
         </is>
       </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t>Le rachat des BCRL – Série 1 effectué le 17 novembre 2025 a été pris en compte dans les ratios au 31 octobre 2025.</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>Cette note a été ajoutée pour préciser l'impact d'un rachat spécifique sur les ratios de fonds propres, ce qui est important pour l'analyse de la structure du capital.</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>Non</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Sans objet</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>La note de bas de page 'Sans objet' a été ajoutée dans le tableau des exigences de déclaration relatives au ratio de liquidité à court terme pour le trimestre en cours. Cette note semble indiquer qu'il n'y a pas de contenu spécifique à divulguer pour un élément particulier du tableau, ce qui est souvent utilisé pour clarifier l'absence de données ou de conditions applicables.
+L'impact métier de cette note est généralement faible, car elle ne modifie pas les calculs ou les divulgations existantes. Elle sert principalement à éviter toute confusion potentielle concernant l'absence de données ou de conditions spécifiques. Dans le contexte réglementaire, cela n'affecte pas directement les exigences de Bâle III ou les directives du BSIF, car il s'agit d'une clarification plutôt que d'une modification des données ou des méthodologies.
+Il s'agit d'une mise à jour ordinaire visant à clarifier le contenu du tableau. L'analyste devrait confirmer que cette note n'introduit pas de nouvelles exigences ou interprétations qui pourraient affecter d'autres sections du rapport. Aucune action supplémentaire n'est nécessaire à moins que d'autres incohérences ne soient identifiées.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Gestion des risques</t>
+          <t>Gestion du capital</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Exigences de déclaration relatives au ratio de liquidité à court terme (1) (2)</t>
+          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>26</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1959,7 +1811,9 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>Cette note a été ajoutée pour indiquer qu'aucune information supplémentaire n'est requise, ce qui est une clarification cosmétique sans impact significatif sur l'analyse.</t>
+          <t>La note de bas de page 'Sans objet' a été ajoutée dans le tableau des exigences réglementaires des ratios de fonds propres, de levier et TLAC au T1 2026.
+Cette note semble indiquer qu'une section ou un élément du tableau n'est pas applicable pour la période en cours. Cela pourrait être lié à une modification des exigences réglementaires ou à une simplification des divulgations pour cette période spécifique. Cependant, l'absence de contexte supplémentaire rend difficile l'évaluation de son impact direct sur les ratios ou les exigences réglementaires.
+Il s'agit probablement d'une mise à jour ordinaire visant à clarifier l'inapplicabilité d'une section. L'analyste devrait confirmer que cette note n'affecte pas d'autres divulgations ou calculs dans le rapport.</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1980,17 +1834,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Exigences – Ratios des fonds propres (1), de levier (1) et TLAC (2) réglementaires</t>
+          <t>Indicateurs – Banques d’importance systémique mondiale (BISM) (1)</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2006,12 +1860,14 @@
       <c r="G25" s="4" t="inlineStr"/>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Sans objet</t>
+          <t>Pour les exercices terminés les 31 octobre 2025 et 2024.</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Cette note a été ajoutée pour indiquer qu'une section ou un élément n'est plus applicable, ce qui est une mise à jour cosmétique sans impact matériel.</t>
+          <t>La note de bas de page n°7 a été ajoutée dans le tableau des indicateurs BISM pour préciser les périodes de rapport couvertes, à savoir les exercices terminés les 31 octobre 2025 et 2024.
+Ce type de note est généralement utilisé pour clarifier les périodes de temps auxquelles les données du tableau se rapportent. Cela est important pour assurer la transparence et la compréhension des utilisateurs du rapport, mais n'a pas d'impact direct sur les calculs ou les méthodologies sous-jacentes.
+Il s'agit d'une mise à jour ordinaire qui ne nécessite pas d'investigation approfondie. L'analyste peut confirmer que cette note est en ligne avec les pratiques habituelles de mise à jour des périodes de rapport.</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -2020,21 +1876,9 @@
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:01:51.628515+00:00</t>
-        </is>
-      </c>
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2064,22 +1908,20 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Modification</t>
+          <t>Suppression</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Représente la mesure dans laquelle les services de la Banque pourraient être remplacés par ceux d’autres institutions.</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>Pour les exercices terminés les 31 octobre 2025 et 2024.</t>
-        </is>
-      </c>
+          <t>Pour les exercices terminés les 31 octobre 2024 et 2023.</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>Bien que la note soit maintenant une simple référence temporelle, elle ne fournit plus d'informations sur la substituabilité, ce qui réduit la clarté sur ce point.</t>
+          <t>La note de bas de page n°8, qui précisait que les données couvraient les exercices terminés les 31 octobre 2024 et 2023, a été supprimée dans le tableau des indicateurs BISM.
+Cette note servait à indiquer les périodes de temps spécifiques auxquelles les données du tableau se rapportaient. Sa suppression est probablement due à la mise à jour des périodes de rapport pour refléter les années plus récentes, ce qui est une pratique courante dans les rapports financiers.
+Il s'agit d'une mise à jour ordinaire qui ne nécessite pas d'investigation approfondie. L'analyste peut confirmer que cette suppression est en ligne avec les pratiques habituelles de mise à jour des périodes de rapport.</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -2088,21 +1930,9 @@
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
-      <c r="L26" s="4" t="inlineStr">
-        <is>
-          <t>Validé</t>
-        </is>
-      </c>
-      <c r="M26" s="4" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:04:50.682519+00:00</t>
-        </is>
-      </c>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2144,21 +1974,9 @@
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr"/>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>Rejeté</t>
-        </is>
-      </c>
-      <c r="M27" s="4" t="inlineStr">
-        <is>
-          <t>analyst</t>
-        </is>
-      </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>2026-04-18T18:04:17.454250+00:00</t>
-        </is>
-      </c>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N27"/>
